--- a/GITHUB_API TESTING.xlsx
+++ b/GITHUB_API TESTING.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28014"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SDET\03_API Testing\TEST CASES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASHISH\CSE\01_SDET\Projects\API Project\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA54EB8E-FFB4-49AA-9A98-22B3665ECD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625C4369-D351-452B-AC8A-E0B8F579EDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -475,6 +475,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -537,9 +540,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -839,117 +839,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="14" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="17" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="17"/>
     </row>
     <row r="3" spans="1:11" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="14" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="17"/>
     </row>
     <row r="4" spans="1:11" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="14" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="20"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="21"/>
     </row>
     <row r="6" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="27"/>
     </row>
     <row r="7" spans="1:11" ht="29.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="12" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="13"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" spans="1:11" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
@@ -1122,7 +1122,7 @@
       <c r="J12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="27" t="s">
+      <c r="K12" s="6" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1140,36 +1140,36 @@
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:11" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="12" t="s">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="13"/>
+      <c r="K15" s="14"/>
     </row>
     <row r="16" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
@@ -1405,9 +1405,7 @@
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="1">
-        <v>11</v>
-      </c>
+      <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -1420,9 +1418,7 @@
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="1">
-        <v>12</v>
-      </c>
+      <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -1435,9 +1431,7 @@
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="1">
-        <v>13</v>
-      </c>
+      <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -1450,9 +1444,7 @@
       <c r="K25" s="1"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="1">
-        <v>15</v>
-      </c>
+      <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -1465,9 +1457,7 @@
       <c r="K26" s="1"/>
     </row>
     <row r="27" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="1">
-        <v>16</v>
-      </c>
+      <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -1480,9 +1470,7 @@
       <c r="K27" s="1"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="1">
-        <v>17</v>
-      </c>
+      <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -1495,9 +1483,7 @@
       <c r="K28" s="1"/>
     </row>
     <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="1">
-        <v>18</v>
-      </c>
+      <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -1510,9 +1496,7 @@
       <c r="K29" s="1"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="1">
-        <v>19</v>
-      </c>
+      <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -1525,9 +1509,7 @@
       <c r="K30" s="1"/>
     </row>
     <row r="31" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="1">
-        <v>20</v>
-      </c>
+      <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -1540,9 +1522,7 @@
       <c r="K31" s="1"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="1">
-        <v>25</v>
-      </c>
+      <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -1555,9 +1535,7 @@
       <c r="K32" s="1"/>
     </row>
     <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="1">
-        <v>26</v>
-      </c>
+      <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -1570,9 +1548,7 @@
       <c r="K33" s="1"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="1">
-        <v>27</v>
-      </c>
+      <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
